--- a/out/gpt_20260430_excel.xlsx
+++ b/out/gpt_20260430_excel.xlsx
@@ -474,8 +474,16 @@
           <t>13:07:42</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.6亿</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>11.52%</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>公告</t>
@@ -503,8 +511,16 @@
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>9.01亿</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16.65%</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>公告</t>
@@ -532,8 +548,16 @@
           <t>09:33:45</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.85亿</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>公告</t>
@@ -561,8 +585,16 @@
           <t>09:47:00</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.91亿</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>4.22%</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>公告</t>
@@ -590,8 +622,16 @@
           <t>10:04:15</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11.72亿</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>8.19%</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>公告</t>
@@ -619,8 +659,16 @@
           <t>10:06:30</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.45亿</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>6.08%</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>公告</t>
@@ -648,8 +696,16 @@
           <t>10:22:19</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8.12亿</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9.82%</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>公告</t>
@@ -677,8 +733,16 @@
           <t>10:49:18</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.81亿</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>29.7%</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>公告</t>
@@ -706,8 +770,16 @@
           <t>14:01:00</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>33.58亿</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>32.77%</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>公告</t>
@@ -735,8 +807,16 @@
           <t>14:28:20</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>28.27亿</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>21.01%</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>公告</t>
@@ -764,8 +844,16 @@
           <t>14:30:09</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>10.19亿</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8.01%</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>公告</t>
@@ -789,8 +877,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>8222.32万</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>公告</t>
@@ -814,8 +910,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6907.2万</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2.12%</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>公告</t>
@@ -839,8 +943,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.13亿</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.79%</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>公告</t>
@@ -864,8 +976,16 @@
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2.57亿</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4.55%</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>公告</t>
@@ -889,8 +1009,16 @@
           <t>09:31:31</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.14亿</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>3.27%</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>公告</t>
@@ -914,8 +1042,16 @@
           <t>09:33:03</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.43亿</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2.48%</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>公告</t>
@@ -939,8 +1075,16 @@
           <t>09:33:48</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.08亿</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>3.03%</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>公告</t>
@@ -964,8 +1108,16 @@
           <t>09:34:11</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>7.96亿</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>7.03%</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>公告</t>
@@ -989,8 +1141,16 @@
           <t>09:37:38</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.15亿</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>5.29%</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1014,8 +1174,16 @@
           <t>09:38:10</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>7.19亿</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5.58%</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1039,8 +1207,16 @@
           <t>09:40:46</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.99亿</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1064,8 +1240,16 @@
           <t>09:43:37</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.6亿</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8.1%</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1089,8 +1273,16 @@
           <t>09:44:03</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2.18亿</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>3.71%</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1114,8 +1306,16 @@
           <t>09:47:43</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8.9亿</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2.33%</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1139,8 +1339,16 @@
           <t>09:49:33</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2.1亿</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>7.49%</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1164,8 +1372,16 @@
           <t>09:50:40</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.52亿</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>13.09%</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1189,8 +1405,16 @@
           <t>09:53:06</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2.16亿</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1214,8 +1438,16 @@
           <t>10:00:48</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>5.6亿</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4.39%</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1239,8 +1471,16 @@
           <t>10:09:54</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2.43亿</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4.67%</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1264,8 +1504,16 @@
           <t>10:23:18</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23.55亿</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>5.36%</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1289,8 +1537,16 @@
           <t>10:36:37</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>7.17亿</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1314,8 +1570,16 @@
           <t>10:57:49</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>18.55亿</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>11.23%</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1339,8 +1603,16 @@
           <t>13:02:28</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>9.32亿</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>6.08%</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1364,8 +1636,16 @@
           <t>13:07:18</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.79亿</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>9.62%</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1389,8 +1669,16 @@
           <t>14:56:21</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>40.4亿</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>26.83%</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1410,8 +1698,16 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>6.68亿</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.83%</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1431,8 +1727,16 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>6.34亿</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>5.79%</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>公告</t>
@@ -1460,8 +1764,16 @@
           <t>13:34:42</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>32.2亿</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>21.77%</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1489,8 +1801,16 @@
           <t>13:12:26</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>18.12亿</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>8.67%</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1514,8 +1834,16 @@
           <t>10:16:27</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>83.21亿</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>13.38%</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1539,8 +1867,16 @@
           <t>10:51:45</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>11.72亿</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>9.7%</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1564,8 +1900,16 @@
           <t>13:27:15</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2.56亿</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4.91%</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1589,8 +1933,16 @@
           <t>13:32:36</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>4.1亿</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2.89%</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1614,8 +1966,16 @@
           <t>13:44:37</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>284.66亿</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>4.24%</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1639,8 +1999,16 @@
           <t>14:15:03</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>12.21亿</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>13.76%</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1664,8 +2032,16 @@
           <t>14:25:33</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>11.54亿</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>12.64%</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>国产芯片</t>
@@ -1693,8 +2069,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.69亿</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1.7%</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1722,8 +2106,16 @@
           <t>10:49:18</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>36.46亿</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>13.06%</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1751,8 +2143,16 @@
           <t>09:30:09</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2.97亿</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>4.68%</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1780,8 +2180,16 @@
           <t>14:42:45</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>11.76亿</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>12.14%</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1805,8 +2213,16 @@
           <t>09:54:29</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2.34亿</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>6.38%</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1830,8 +2246,16 @@
           <t>13:41:42</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19.73亿</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>14.37%</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1855,8 +2279,16 @@
           <t>14:30:09</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>52.39亿</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9.74%</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>电池产业链</t>
@@ -1884,8 +2316,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>9542.22万</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>算力</t>
@@ -1909,8 +2349,16 @@
           <t>09:42:06</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>6.24亿</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8.54%</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>算力</t>
@@ -1934,8 +2382,16 @@
           <t>11:09:04</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>111.24亿</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>7.78%</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>算力</t>
@@ -1959,8 +2415,16 @@
           <t>13:49:51</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21.25亿</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>6.27%</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>算力</t>
@@ -1984,8 +2448,16 @@
           <t>14:40:15</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17.64亿</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>14.25%</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>算力</t>
@@ -2005,8 +2477,16 @@
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>11亿</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>18.66%</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>算力</t>
@@ -2026,8 +2506,16 @@
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>113.27亿</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10.29%</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>算力</t>
@@ -2055,8 +2543,16 @@
           <t>14:34:53</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>5.09亿</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>8.35%</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2080,8 +2576,16 @@
           <t>10:02:05</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>4.58亿</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10.26%</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2105,8 +2609,16 @@
           <t>10:35:54</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>7.51亿</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>16.71%</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2130,8 +2642,16 @@
           <t>13:12:08</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>21.98亿</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2155,8 +2675,16 @@
           <t>13:18:21</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>4.06亿</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>8.19%</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2180,8 +2708,16 @@
           <t>13:20:00</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>5.14亿</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>4.94%</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>机器人</t>
@@ -2205,8 +2741,16 @@
           <t>10:29:25</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3.24亿</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>商业航天</t>
@@ -2230,8 +2774,16 @@
           <t>10:57:27</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>46.84亿</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>15.66%</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>商业航天</t>
@@ -2255,8 +2807,16 @@
           <t>13:25:33</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20.76亿</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>9.05%</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>商业航天</t>
@@ -2280,8 +2840,16 @@
           <t>13:41:13</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>7.28亿</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>5.1%</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>商业航天</t>
@@ -2305,8 +2873,16 @@
           <t>13:50:00</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.77亿</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>7.08%</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>商业航天</t>
@@ -2334,8 +2910,16 @@
           <t>09:39:23</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5.93亿</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>5.66%</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>体育产业</t>
@@ -2363,8 +2947,16 @@
           <t>09:50:54</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>3.48亿</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1.83%</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>体育产业</t>
@@ -2392,8 +2984,16 @@
           <t>09:52:45</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>12.02亿</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>6.64%</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>体育产业</t>
@@ -2417,8 +3017,16 @@
           <t>13:25:18</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>11.71亿</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>19.14%</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>体育产业</t>
@@ -2442,8 +3050,16 @@
           <t>13:10:05</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.85亿</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>6.18%</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>地产</t>
@@ -2463,8 +3079,16 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>3.49亿</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr">
         <is>
           <t>地产</t>
@@ -2492,8 +3116,16 @@
           <t>09:53:56</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>7.34亿</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>13.28%</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2521,8 +3153,16 @@
           <t>13:13:13</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>10.18亿</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>16.46%</t>
+        </is>
+      </c>
       <c r="G81" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2546,8 +3186,16 @@
           <t>13:19:26</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.38亿</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6.54%</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2571,8 +3219,16 @@
           <t>13:32:33</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>1.73亿</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>3.35%</t>
+        </is>
+      </c>
       <c r="G83" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2596,8 +3252,16 @@
           <t>13:50:50</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2.7亿</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>9.64%</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2621,8 +3285,16 @@
           <t>14:22:24</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>4.35亿</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10.1%</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2642,8 +3314,16 @@
       </c>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>9.21亿</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>5.68%</t>
+        </is>
+      </c>
       <c r="G86" t="inlineStr">
         <is>
           <t>其他</t>
@@ -2663,8 +3343,16 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>22.09亿</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>77.24%</t>
+        </is>
+      </c>
       <c r="G87" t="inlineStr">
         <is>
           <t>新股</t>
@@ -2692,8 +3380,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>4234.72万</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1.01%</t>
+        </is>
+      </c>
       <c r="G88" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2721,8 +3417,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>392.28万</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2750,8 +3454,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>1559.7万</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0.16%</t>
+        </is>
+      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2779,8 +3491,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1258.17万</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2808,8 +3528,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>842.27万</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2837,8 +3565,16 @@
           <t>09:30:00</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>3306.89万</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1.61%</t>
+        </is>
+      </c>
       <c r="G93" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2866,8 +3602,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>1600.97万</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2895,8 +3639,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>555.72万</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2924,8 +3676,16 @@
           <t>10:06:27</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>1.22亿</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>5.24%</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2949,8 +3709,16 @@
           <t>09:25:00</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>6692.68万</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>3.92%</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2974,8 +3742,16 @@
           <t>09:25:01</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2992.21万</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0.55%</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -2999,8 +3775,16 @@
           <t>10:16:39</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2.64亿</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>14.85%</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3024,8 +3808,16 @@
           <t>10:19:18</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>4559.84万</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3049,8 +3841,16 @@
           <t>10:20:17</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9128.51万</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>5.07%</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3074,8 +3874,16 @@
           <t>10:27:27</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>7.98亿</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2.85%</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3099,8 +3907,16 @@
           <t>11:12:40</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>6565.19万</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2.17%</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3124,8 +3940,16 @@
           <t>14:00:51</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>1.53亿</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>8.68%</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3149,8 +3973,16 @@
           <t>14:06:59</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>1.78亿</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1.12%</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3174,8 +4006,16 @@
           <t>14:54:42</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5578.86万</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2.1%</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3195,8 +4035,16 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>1.87亿</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3216,8 +4064,16 @@
       </c>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>8848.14万</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>3.95%</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>ST板块</t>
@@ -3237,8 +4093,16 @@
       </c>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>1.4亿</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>5.49%</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
           <t>ST板块</t>
